--- a/products_database.xlsx
+++ b/products_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F82BC7C-AA27-4121-9D90-A6753430F81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E434DDB-AB6A-4BA0-B316-DF5F30FDD6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
